--- a/Client Reporting Kit/02_Client_Report_Template.xlsx
+++ b/Client Reporting Kit/02_Client_Report_Template.xlsx
@@ -12,11 +12,12 @@
     <sheet name="Executive Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Performance" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Platform Detail" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Top Ads" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Creatives" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Weekly Trend" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="What We Did &amp; Next" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Dictionary" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Combined" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Top Ads" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Creatives" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Weekly Trend" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="What We Did &amp; Next" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Dictionary" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,12 +26,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0.00&quot; EGP&quot;"/>
     <numFmt numFmtId="166" formatCode="0.000&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="+0.0%;-0.0%"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -161,6 +163,11 @@
       <name val="Inter"/>
       <i val="1"/>
       <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Inter"/>
+      <color rgb="00C2410C"/>
       <sz val="9"/>
     </font>
     <font>
@@ -303,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -495,22 +502,37 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="24" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="23" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="24" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -520,7 +542,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1794,6 +1816,223 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>What we did, and what happens next</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="32">
+        <f>_Inputs!$B$5&amp;"   ·   the part of the report the client actually reads"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WHAT WE CHANGED THIS MONTH</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="84" t="inlineStr">
+        <is>
+          <t>What we changed this month</t>
+        </is>
+      </c>
+      <c r="B5" s="85">
+        <f>_Inputs!$B$56</f>
+        <v/>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Name three things you actually did. Specifics beat adjectives: "launched four UGC concepts" not "optimised creative".</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1"/>
+    <row r="7" ht="20" customHeight="1"/>
+    <row r="8" ht="20" customHeight="1"/>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WHAT WE LEARNED</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="84" t="inlineStr">
+        <is>
+          <t>What we learned</t>
+        </is>
+      </c>
+      <c r="B11" s="85">
+        <f>_Inputs!$B$57</f>
+        <v/>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>One insight the data proved. This is what you are paid for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1"/>
+    <row r="14" ht="20" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WHAT WE ARE DOING NEXT MONTH</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="84" t="inlineStr">
+        <is>
+          <t>What we are doing next month</t>
+        </is>
+      </c>
+      <c r="B17" s="85">
+        <f>_Inputs!$B$58</f>
+        <v/>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Two or three concrete moves, each tied to a number above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WHAT THE NUMBERS DON'T SHOW</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="84" t="inlineStr">
+        <is>
+          <t>What the numbers don't show</t>
+        </is>
+      </c>
+      <c r="B23" s="85">
+        <f>_Inputs!$B$59</f>
+        <v/>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Stockouts, shipping delays, a price change, a competitor entering. Say it before the client finds it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1"/>
+    <row r="25" ht="20" customHeight="1"/>
+    <row r="26" ht="20" customHeight="1"/>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WHAT WE NEED FROM YOU</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="84" t="inlineStr">
+        <is>
+          <t>What we need from you</t>
+        </is>
+      </c>
+      <c r="B29" s="85">
+        <f>_Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>One clear ask. New imagery, a price decision, a stock fix. Give them a job and they become a partner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1"/>
+    <row r="31" ht="20" customHeight="1"/>
+    <row r="32" ht="20" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HOW TO FILL THESE IN</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="46" customHeight="1">
+      <c r="A35" s="56" t="inlineStr">
+        <is>
+          <t>Don't write these from scratch.</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Open 05_AI_Prompts_Campaign_Performance.md and run Prompt 1 (the monthly narrative) on your _Inputs tab. It will draft all five blocks. Then edit for tone — delete anything that sounds like a machine, and cut it to half the length. The client reads the first sentence of each block.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="56" t="inlineStr">
+        <is>
+          <t>The tone rule</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>Never explain a metric the client didn't ask about. Never hide a bad month. Lead with what changed and what you're doing about it — the numbers are evidence, not the message.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="C17:C20"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="C29:C32"/>
+    <mergeCell ref="B29:B32"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="C23:C26"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A34:B34"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1834,296 +2073,296 @@
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="81" t="inlineStr">
+      <c r="A5" s="86" t="inlineStr">
         <is>
           <t>Ad spend</t>
         </is>
       </c>
-      <c r="B5" s="82" t="inlineStr">
+      <c r="B5" s="87" t="inlineStr">
         <is>
           <t>What we put into Meta and TikTok this month.</t>
         </is>
       </c>
-      <c r="C5" s="82" t="inlineStr">
+      <c r="C5" s="87" t="inlineStr">
         <is>
           <t>This is the investment. Everything else is the result of it.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="81" t="inlineStr">
+      <c r="A6" s="86" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="B6" s="82" t="inlineStr">
+      <c r="B6" s="87" t="inlineStr">
         <is>
           <t>How many times our ads were shown.</t>
         </is>
       </c>
-      <c r="C6" s="82" t="inlineStr">
+      <c r="C6" s="87" t="inlineStr">
         <is>
           <t>Volume of attention — not a result on its own.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="81" t="inlineStr">
+      <c r="A7" s="86" t="inlineStr">
         <is>
           <t>Reach</t>
         </is>
       </c>
-      <c r="B7" s="82" t="inlineStr">
+      <c r="B7" s="87" t="inlineStr">
         <is>
           <t>How many people saw the ads (counted once per person per day).</t>
         </is>
       </c>
-      <c r="C7" s="82" t="inlineStr">
+      <c r="C7" s="87" t="inlineStr">
         <is>
           <t>How many humans, roughly. It can't be added up across a month, so treat it as a trend.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="81" t="inlineStr">
+      <c r="A8" s="86" t="inlineStr">
         <is>
           <t>Frequency</t>
         </is>
       </c>
-      <c r="B8" s="82" t="inlineStr">
+      <c r="B8" s="87" t="inlineStr">
         <is>
           <t>How many times, on average, each person saw us.</t>
         </is>
       </c>
-      <c r="C8" s="82" t="inlineStr">
+      <c r="C8" s="87" t="inlineStr">
         <is>
           <t>Too low and you're under-spending; too high and people stop noticing us.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="81" t="inlineStr">
+      <c r="A9" s="86" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="B9" s="82" t="inlineStr">
+      <c r="B9" s="87" t="inlineStr">
         <is>
           <t>What it cost to show our ads a thousand times.</t>
         </is>
       </c>
-      <c r="C9" s="82" t="inlineStr">
+      <c r="C9" s="87" t="inlineStr">
         <is>
           <t>The price of attention. It rises and falls with auction competition, not just our choices.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="81" t="inlineStr">
+      <c r="A10" s="86" t="inlineStr">
         <is>
           <t>CTR</t>
         </is>
       </c>
-      <c r="B10" s="82" t="inlineStr">
+      <c r="B10" s="87" t="inlineStr">
         <is>
           <t>The share of people who clicked after seeing an ad.</t>
         </is>
       </c>
-      <c r="C10" s="82" t="inlineStr">
+      <c r="C10" s="87" t="inlineStr">
         <is>
           <t>How well the creative earns attention.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="81" t="inlineStr">
+      <c r="A11" s="86" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="B11" s="82" t="inlineStr">
+      <c r="B11" s="87" t="inlineStr">
         <is>
           <t>Visits to your site from our ads.</t>
         </is>
       </c>
-      <c r="C11" s="82" t="inlineStr">
+      <c r="C11" s="87" t="inlineStr">
         <is>
           <t>The top of your sales funnel.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="81" t="inlineStr">
+      <c r="A12" s="86" t="inlineStr">
         <is>
           <t>Add to cart</t>
         </is>
       </c>
-      <c r="B12" s="82" t="inlineStr">
+      <c r="B12" s="87" t="inlineStr">
         <is>
           <t>People who put something in their basket.</t>
         </is>
       </c>
-      <c r="C12" s="82" t="inlineStr">
+      <c r="C12" s="87" t="inlineStr">
         <is>
           <t>Intent. This is where we see if the product page is doing its job.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="81" t="inlineStr">
+      <c r="A13" s="86" t="inlineStr">
         <is>
           <t>Initiate checkout</t>
         </is>
       </c>
-      <c r="B13" s="82" t="inlineStr">
+      <c r="B13" s="87" t="inlineStr">
         <is>
           <t>People who started checking out.</t>
         </is>
       </c>
-      <c r="C13" s="82" t="inlineStr">
+      <c r="C13" s="87" t="inlineStr">
         <is>
           <t>The last step before money moves.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="34" customHeight="1">
-      <c r="A14" s="81" t="inlineStr">
+      <c r="A14" s="86" t="inlineStr">
         <is>
           <t>Purchases</t>
         </is>
       </c>
-      <c r="B14" s="82" t="inlineStr">
+      <c r="B14" s="87" t="inlineStr">
         <is>
           <t>Orders attributed to our ads.</t>
         </is>
       </c>
-      <c r="C14" s="82" t="inlineStr">
+      <c r="C14" s="87" t="inlineStr">
         <is>
           <t>The result we're judged on — reported inside the platform's attribution window, which is stated on every report.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="81" t="inlineStr">
+      <c r="A15" s="86" t="inlineStr">
         <is>
           <t>Purchases value / Revenue</t>
         </is>
       </c>
-      <c r="B15" s="82" t="inlineStr">
+      <c r="B15" s="87" t="inlineStr">
         <is>
           <t>The value of those orders.</t>
         </is>
       </c>
-      <c r="C15" s="82" t="inlineStr">
+      <c r="C15" s="87" t="inlineStr">
         <is>
           <t>This is what ROAS is built from.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="81" t="inlineStr">
+      <c r="A16" s="86" t="inlineStr">
         <is>
           <t>ROAS</t>
         </is>
       </c>
-      <c r="B16" s="82" t="inlineStr">
+      <c r="B16" s="87" t="inlineStr">
         <is>
           <t>Revenue divided by ad spend. A 3.0x return means each unit spent brought back 3.</t>
         </is>
       </c>
-      <c r="C16" s="82" t="inlineStr">
+      <c r="C16" s="87" t="inlineStr">
         <is>
           <t>The headline efficiency number.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="81" t="inlineStr">
+      <c r="A17" s="86" t="inlineStr">
         <is>
           <t>Breakeven ROAS</t>
         </is>
       </c>
-      <c r="B17" s="82" t="inlineStr">
+      <c r="B17" s="87" t="inlineStr">
         <is>
           <t>The ROAS at which you make exactly zero profit after product cost, shipping, fees and returns.</t>
         </is>
       </c>
-      <c r="C17" s="82" t="inlineStr">
+      <c r="C17" s="87" t="inlineStr">
         <is>
           <t>The only number that tells you whether a ROAS is good. A 3x ROAS is a loss for one business and a win for another.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="81" t="inlineStr">
+      <c r="A18" s="86" t="inlineStr">
         <is>
           <t>AOV</t>
         </is>
       </c>
-      <c r="B18" s="82" t="inlineStr">
+      <c r="B18" s="87" t="inlineStr">
         <is>
           <t>Average order value.</t>
         </is>
       </c>
-      <c r="C18" s="82" t="inlineStr">
+      <c r="C18" s="87" t="inlineStr">
         <is>
           <t>A rising AOV can rescue a rising cost per order.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="81" t="inlineStr">
+      <c r="A19" s="86" t="inlineStr">
         <is>
           <t>Cost per purchase</t>
         </is>
       </c>
-      <c r="B19" s="82" t="inlineStr">
+      <c r="B19" s="87" t="inlineStr">
         <is>
           <t>Ad spend divided by orders.</t>
         </is>
       </c>
-      <c r="C19" s="82" t="inlineStr">
+      <c r="C19" s="87" t="inlineStr">
         <is>
           <t>Meaningful only next to AOV and breakeven. Cheaper orders from a lower-value basket aren't progress.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="81" t="inlineStr">
+      <c r="A20" s="86" t="inlineStr">
         <is>
           <t>Conversion rate</t>
         </is>
       </c>
-      <c r="B20" s="82" t="inlineStr">
+      <c r="B20" s="87" t="inlineStr">
         <is>
           <t>The share of clicks that became orders.</t>
         </is>
       </c>
-      <c r="C20" s="82" t="inlineStr">
+      <c r="C20" s="87" t="inlineStr">
         <is>
           <t>How well the site converts the traffic we buy.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="81" t="inlineStr">
+      <c r="A21" s="86" t="inlineStr">
         <is>
           <t>Attribution window</t>
         </is>
       </c>
-      <c r="B21" s="82" t="inlineStr">
+      <c r="B21" s="87" t="inlineStr">
         <is>
           <t>How long after clicking a platform still credits itself with a sale.</t>
         </is>
       </c>
-      <c r="C21" s="82" t="inlineStr">
+      <c r="C21" s="87" t="inlineStr">
         <is>
           <t>We keep this fixed month to month so comparisons stay honest. It's stated on the report.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="83">
+      <c r="A23" s="88">
         <f>"All figures are pulled directly from Meta's and TikTok's own reporting APIs. There is no manual entry step between the platform and this report."</f>
         <v/>
       </c>
@@ -3645,7 +3884,7 @@
         <v/>
       </c>
       <c r="H13" s="51">
-        <f>_Inputs!$C$46</f>
+        <f>_Inputs!$C$45</f>
         <v/>
       </c>
     </row>
@@ -3701,7 +3940,7 @@
         <v/>
       </c>
       <c r="H15" s="48">
-        <f>_Inputs!$C$48</f>
+        <f>_Inputs!$C$47</f>
         <v/>
       </c>
     </row>
@@ -3801,6 +4040,689 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>Combined — Meta + TikTok</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="32">
+        <f>_Inputs!$B$5&amp;"   ·   "&amp;_Inputs!$B$6&amp;" against "&amp;_Inputs!$B$7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="73" t="inlineStr">
+        <is>
+          <t>This is the only tab where the two platforms share a row — everything else keeps them apart on purpose, so a weak channel cannot hide behind a strong one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE TWO PLATFORMS TOGETHER</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="45" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C6" s="46" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="D6" s="46" t="inlineStr">
+        <is>
+          <t>Combined</t>
+        </is>
+      </c>
+      <c r="E6" s="46" t="inlineStr">
+        <is>
+          <t>Meta share</t>
+        </is>
+      </c>
+      <c r="F6" s="46" t="inlineStr">
+        <is>
+          <t>TikTok share</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="64" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="B7" s="65">
+        <f>_Inputs!$B$22</f>
+        <v/>
+      </c>
+      <c r="C7" s="65">
+        <f>_Inputs!$B$38</f>
+        <v/>
+      </c>
+      <c r="D7" s="65">
+        <f>_Inputs!$D$13</f>
+        <v/>
+      </c>
+      <c r="E7" s="74">
+        <f>IFERROR(B7/D7,"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="74">
+        <f>IFERROR(C7/D7,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="64" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="B8" s="67">
+        <f>_Inputs!$B$24</f>
+        <v/>
+      </c>
+      <c r="C8" s="67">
+        <f>_Inputs!$B$41</f>
+        <v/>
+      </c>
+      <c r="D8" s="67">
+        <f>B8+C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="74">
+        <f>IFERROR(B8/D8,"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="74">
+        <f>IFERROR(C8/D8,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="64" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="B9" s="67">
+        <f>_Inputs!$B$23*_Inputs!$B$24</f>
+        <v/>
+      </c>
+      <c r="C9" s="67">
+        <f>_Inputs!$B$40*_Inputs!$B$41</f>
+        <v/>
+      </c>
+      <c r="D9" s="67">
+        <f>B9+C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="74">
+        <f>IFERROR(B9/D9,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="74">
+        <f>IFERROR(C9/D9,"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="73" t="inlineStr">
+        <is>
+          <t>derived: CTR × impressions (the automation payload has no click column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="64" t="inlineStr">
+        <is>
+          <t>Adds to cart</t>
+        </is>
+      </c>
+      <c r="B10" s="67">
+        <f>_Inputs!$B$27</f>
+        <v/>
+      </c>
+      <c r="C10" s="67">
+        <f>_Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="D10" s="67">
+        <f>B10+C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="64" t="inlineStr">
+        <is>
+          <t>Initiate Checkout</t>
+        </is>
+      </c>
+      <c r="B11" s="67">
+        <f>_Inputs!$B$28</f>
+        <v/>
+      </c>
+      <c r="C11" s="67">
+        <f>_Inputs!$B$45</f>
+        <v/>
+      </c>
+      <c r="D11" s="67">
+        <f>B11+C11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="64" t="inlineStr">
+        <is>
+          <t>Purchases</t>
+        </is>
+      </c>
+      <c r="B12" s="67">
+        <f>_Inputs!$B$29</f>
+        <v/>
+      </c>
+      <c r="C12" s="67">
+        <f>_Inputs!$B$46</f>
+        <v/>
+      </c>
+      <c r="D12" s="67">
+        <f>_Inputs!$D$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="64" t="inlineStr">
+        <is>
+          <t>Purchases Value</t>
+        </is>
+      </c>
+      <c r="B13" s="65">
+        <f>_Inputs!$B$31</f>
+        <v/>
+      </c>
+      <c r="C13" s="65">
+        <f>_Inputs!$B$48</f>
+        <v/>
+      </c>
+      <c r="D13" s="65">
+        <f>_Inputs!$D$16</f>
+        <v/>
+      </c>
+      <c r="E13" s="74">
+        <f>IFERROR(B13/D13,"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="74">
+        <f>IFERROR(C13/D13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="64" t="inlineStr">
+        <is>
+          <t>Reach (sum of days)</t>
+        </is>
+      </c>
+      <c r="B14" s="67">
+        <f>_Inputs!$B$25</f>
+        <v/>
+      </c>
+      <c r="C14" s="67">
+        <f>_Inputs!$B$42</f>
+        <v/>
+      </c>
+      <c r="D14" s="67">
+        <f>B14+C14</f>
+        <v/>
+      </c>
+      <c r="G14" s="73" t="inlineStr">
+        <is>
+          <t>sum of daily reach — a trend, not a headcount</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="64" t="inlineStr">
+        <is>
+          <t>CPM</t>
+        </is>
+      </c>
+      <c r="B15" s="65">
+        <f>IFERROR(_Inputs!$B$22/_Inputs!$B$24*1000,0)</f>
+        <v/>
+      </c>
+      <c r="C15" s="65">
+        <f>_Inputs!$B$39</f>
+        <v/>
+      </c>
+      <c r="D15" s="65">
+        <f>IFERROR(D7/D8*1000,0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="73" t="inlineStr">
+        <is>
+          <t>Meta CPM is derived from spend ÷ impressions</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="64" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="B16" s="49">
+        <f>_Inputs!$B$23</f>
+        <v/>
+      </c>
+      <c r="C16" s="49">
+        <f>_Inputs!$B$40</f>
+        <v/>
+      </c>
+      <c r="D16" s="49">
+        <f>IFERROR(D9/D8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="64" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="B17" s="68">
+        <f>_Inputs!$B$26</f>
+        <v/>
+      </c>
+      <c r="C17" s="68">
+        <f>_Inputs!$B$43</f>
+        <v/>
+      </c>
+      <c r="D17" s="68">
+        <f>IFERROR(D8/D14,0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="73" t="inlineStr">
+        <is>
+          <t>impressions ÷ reach</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="64" t="inlineStr">
+        <is>
+          <t>Cost Per Purchase</t>
+        </is>
+      </c>
+      <c r="B18" s="65">
+        <f>_Inputs!$B$30</f>
+        <v/>
+      </c>
+      <c r="C18" s="65">
+        <f>_Inputs!$B$47</f>
+        <v/>
+      </c>
+      <c r="D18" s="65">
+        <f>_Inputs!$D$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="64" t="inlineStr">
+        <is>
+          <t>ROAS</t>
+        </is>
+      </c>
+      <c r="B19" s="70">
+        <f>_Inputs!$B$32</f>
+        <v/>
+      </c>
+      <c r="C19" s="70">
+        <f>_Inputs!$B$49</f>
+        <v/>
+      </c>
+      <c r="D19" s="70">
+        <f>_Inputs!$D$17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="64" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="B20" s="65">
+        <f>_Inputs!$B$33</f>
+        <v/>
+      </c>
+      <c r="C20" s="65">
+        <f>_Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="D20" s="65">
+        <f>_Inputs!$D$18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  THE COMBINED FUNNEL</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B23" s="46" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="C23" s="46" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="inlineStr">
+        <is>
+          <t>Combined</t>
+        </is>
+      </c>
+      <c r="E23" s="46" t="inlineStr">
+        <is>
+          <t>Step rate</t>
+        </is>
+      </c>
+      <c r="F23" s="46" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="64" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="B24" s="67">
+        <f>_Inputs!$B$24</f>
+        <v/>
+      </c>
+      <c r="C24" s="67">
+        <f>_Inputs!$B$41</f>
+        <v/>
+      </c>
+      <c r="D24" s="67">
+        <f>B24+C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="49">
+        <f>IFERROR(D25/D24,0)</f>
+        <v/>
+      </c>
+      <c r="F24" s="75">
+        <f>REPT("█",ROUND(20*IFERROR(D25/D24,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="64" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="B25" s="67">
+        <f>_Inputs!$B$23*_Inputs!$B$24</f>
+        <v/>
+      </c>
+      <c r="C25" s="67">
+        <f>_Inputs!$B$40*_Inputs!$B$41</f>
+        <v/>
+      </c>
+      <c r="D25" s="67">
+        <f>B25+C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="49">
+        <f>IFERROR(D26/D25,0)</f>
+        <v/>
+      </c>
+      <c r="F25" s="75">
+        <f>REPT("█",ROUND(20*IFERROR(D26/D25,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="64" t="inlineStr">
+        <is>
+          <t>Adds to cart</t>
+        </is>
+      </c>
+      <c r="B26" s="67">
+        <f>_Inputs!$B$27</f>
+        <v/>
+      </c>
+      <c r="C26" s="67">
+        <f>_Inputs!$B$44</f>
+        <v/>
+      </c>
+      <c r="D26" s="67">
+        <f>B26+C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="49">
+        <f>IFERROR(D27/D26,0)</f>
+        <v/>
+      </c>
+      <c r="F26" s="75">
+        <f>REPT("█",ROUND(20*IFERROR(D27/D26,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="64" t="inlineStr">
+        <is>
+          <t>Initiate Checkout</t>
+        </is>
+      </c>
+      <c r="B27" s="67">
+        <f>_Inputs!$B$28</f>
+        <v/>
+      </c>
+      <c r="C27" s="67">
+        <f>_Inputs!$B$45</f>
+        <v/>
+      </c>
+      <c r="D27" s="67">
+        <f>B27+C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="49">
+        <f>IFERROR(D28/D27,0)</f>
+        <v/>
+      </c>
+      <c r="F27" s="75">
+        <f>REPT("█",ROUND(20*IFERROR(D28/D27,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="64" t="inlineStr">
+        <is>
+          <t>Purchases</t>
+        </is>
+      </c>
+      <c r="B28" s="67">
+        <f>_Inputs!$B$29</f>
+        <v/>
+      </c>
+      <c r="C28" s="67">
+        <f>_Inputs!$B$46</f>
+        <v/>
+      </c>
+      <c r="D28" s="67">
+        <f>B28+C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  WHICH PLATFORM IS EARNING ITS KEEP</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="45" t="inlineStr">
+        <is>
+          <t>Platform</t>
+        </is>
+      </c>
+      <c r="B31" s="46" t="inlineStr">
+        <is>
+          <t>Share of spend</t>
+        </is>
+      </c>
+      <c r="C31" s="46" t="inlineStr">
+        <is>
+          <t>Share of revenue</t>
+        </is>
+      </c>
+      <c r="D31" s="46" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="E31" s="46" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="64" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B32" s="49">
+        <f>IFERROR(_Inputs!$B$22/_Inputs!$D$13,0)</f>
+        <v/>
+      </c>
+      <c r="C32" s="49">
+        <f>IFERROR(_Inputs!$B$31/_Inputs!$D$16,0)</f>
+        <v/>
+      </c>
+      <c r="D32" s="76">
+        <f>C32-B32</f>
+        <v/>
+      </c>
+      <c r="E32" s="42">
+        <f>IF(C32=0,"",IF(D32&gt;0.02,"Pulling more than its weight — revenue share is ahead of spend share.",IF(D32&lt;-0.02,"Costing more than it returns — spend share is ahead of revenue share.","Roughly balanced with its budget share.")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="64" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="B33" s="49">
+        <f>IFERROR(_Inputs!$B$38/_Inputs!$D$13,0)</f>
+        <v/>
+      </c>
+      <c r="C33" s="49">
+        <f>IFERROR(_Inputs!$B$48/_Inputs!$D$16,0)</f>
+        <v/>
+      </c>
+      <c r="D33" s="76">
+        <f>C33-B33</f>
+        <v/>
+      </c>
+      <c r="E33" s="42">
+        <f>IF(C33=0,"",IF(D33&gt;0.02,"Pulling more than its weight — revenue share is ahead of spend share.",IF(D33&lt;-0.02,"Costing more than it returns — spend share is ahead of revenue share.","Roughly balanced with its budget share.")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="77">
+        <f>"Blended ROAS is "&amp;ROUND(_Inputs!$D$17,2)&amp;"x. Meta delivered "&amp;ROUND(_Inputs!$B$32,2)&amp;"x on "&amp;TEXT(_Inputs!$B$22/_Inputs!$D$13,"0%")&amp;" of the budget, TikTok "&amp;ROUND(_Inputs!$B$49,2)&amp;"x on "&amp;TEXT(_Inputs!$B$38/_Inputs!$D$13,"0%")&amp;". "&amp;IF(_Inputs!$B$32&gt;_Inputs!$B$49,"Meta is the more efficient channel this period.","TikTok is the more efficient channel this period.")</f>
+        <v/>
+      </c>
+      <c r="B34" s="72" t="n"/>
+      <c r="C34" s="72" t="n"/>
+      <c r="D34" s="72" t="n"/>
+      <c r="E34" s="72" t="n"/>
+      <c r="F34" s="72" t="n"/>
+      <c r="G34" s="72" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3881,21 +4803,21 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="73" t="n">
+      <c r="A6" s="78" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="74" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>VID | Founder story | v4</t>
         </is>
       </c>
-      <c r="C6" s="75" t="n">
+      <c r="C6" s="80" t="n">
         <v>26161</v>
       </c>
-      <c r="D6" s="76" t="n">
+      <c r="D6" s="81" t="n">
         <v>112</v>
       </c>
-      <c r="E6" s="75" t="n">
+      <c r="E6" s="80" t="n">
         <v>76279</v>
       </c>
       <c r="F6" s="70">
@@ -3916,21 +4838,21 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="73" t="n">
+      <c r="A7" s="78" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="74" t="inlineStr">
+      <c r="B7" s="79" t="inlineStr">
         <is>
           <t>STATIC | Bundle offer | v2</t>
         </is>
       </c>
-      <c r="C7" s="75" t="n">
+      <c r="C7" s="80" t="n">
         <v>17134</v>
       </c>
-      <c r="D7" s="76" t="n">
+      <c r="D7" s="81" t="n">
         <v>59</v>
       </c>
-      <c r="E7" s="75" t="n">
+      <c r="E7" s="80" t="n">
         <v>40838</v>
       </c>
       <c r="F7" s="70">
@@ -3951,21 +4873,21 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="73" t="n">
+      <c r="A8" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="74" t="inlineStr">
+      <c r="B8" s="79" t="inlineStr">
         <is>
           <t>UGC | Problem-solution | v2</t>
         </is>
       </c>
-      <c r="C8" s="75" t="n">
+      <c r="C8" s="80" t="n">
         <v>14365</v>
       </c>
-      <c r="D8" s="76" t="n">
+      <c r="D8" s="81" t="n">
         <v>69</v>
       </c>
-      <c r="E8" s="75" t="n">
+      <c r="E8" s="80" t="n">
         <v>42528</v>
       </c>
       <c r="F8" s="70">
@@ -3986,21 +4908,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="73" t="n">
+      <c r="A9" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="74" t="inlineStr">
+      <c r="B9" s="79" t="inlineStr">
         <is>
           <t>VID | Founder story | v3</t>
         </is>
       </c>
-      <c r="C9" s="75" t="n">
+      <c r="C9" s="80" t="n">
         <v>12983</v>
       </c>
-      <c r="D9" s="76" t="n">
+      <c r="D9" s="81" t="n">
         <v>41</v>
       </c>
-      <c r="E9" s="75" t="n">
+      <c r="E9" s="80" t="n">
         <v>28152</v>
       </c>
       <c r="F9" s="70">
@@ -4021,21 +4943,21 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="73" t="n">
+      <c r="A10" s="78" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="74" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>VID | Review compilation | v1</t>
         </is>
       </c>
-      <c r="C10" s="75" t="n">
+      <c r="C10" s="80" t="n">
         <v>12497</v>
       </c>
-      <c r="D10" s="76" t="n">
+      <c r="D10" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="E10" s="75" t="n">
+      <c r="E10" s="80" t="n">
         <v>31048</v>
       </c>
       <c r="F10" s="70">
@@ -4056,21 +4978,21 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="73" t="n">
+      <c r="A11" s="78" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="74" t="inlineStr">
+      <c r="B11" s="79" t="inlineStr">
         <is>
           <t>Spark ad | Creator A</t>
         </is>
       </c>
-      <c r="C11" s="75" t="n">
+      <c r="C11" s="80" t="n">
         <v>10640</v>
       </c>
-      <c r="D11" s="76" t="n">
+      <c r="D11" s="81" t="n">
         <v>63</v>
       </c>
-      <c r="E11" s="75" t="n">
+      <c r="E11" s="80" t="n">
         <v>38122</v>
       </c>
       <c r="F11" s="70">
@@ -4091,21 +5013,21 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="73" t="n">
+      <c r="A12" s="78" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="74" t="inlineStr">
+      <c r="B12" s="79" t="inlineStr">
         <is>
           <t>UGC | Trend audio | v1</t>
         </is>
       </c>
-      <c r="C12" s="75" t="n">
+      <c r="C12" s="80" t="n">
         <v>9684</v>
       </c>
-      <c r="D12" s="76" t="n">
+      <c r="D12" s="81" t="n">
         <v>29</v>
       </c>
-      <c r="E12" s="75" t="n">
+      <c r="E12" s="80" t="n">
         <v>18149</v>
       </c>
       <c r="F12" s="70">
@@ -4126,21 +5048,21 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="73" t="n">
+      <c r="A13" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="74" t="inlineStr">
+      <c r="B13" s="79" t="inlineStr">
         <is>
           <t>STATIC | Bundle offer | v1</t>
         </is>
       </c>
-      <c r="C13" s="75" t="n">
+      <c r="C13" s="80" t="n">
         <v>8631</v>
       </c>
-      <c r="D13" s="76" t="n">
+      <c r="D13" s="81" t="n">
         <v>30</v>
       </c>
-      <c r="E13" s="75" t="n">
+      <c r="E13" s="80" t="n">
         <v>20597</v>
       </c>
       <c r="F13" s="70">
@@ -4161,21 +5083,21 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="73" t="n">
+      <c r="A14" s="78" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="74" t="inlineStr">
+      <c r="B14" s="79" t="inlineStr">
         <is>
           <t>UGC | Trend audio | v2</t>
         </is>
       </c>
-      <c r="C14" s="75" t="n">
+      <c r="C14" s="80" t="n">
         <v>7586</v>
       </c>
-      <c r="D14" s="76" t="n">
+      <c r="D14" s="81" t="n">
         <v>32</v>
       </c>
-      <c r="E14" s="75" t="n">
+      <c r="E14" s="80" t="n">
         <v>19473</v>
       </c>
       <c r="F14" s="70">
@@ -4196,21 +5118,21 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="73" t="n">
+      <c r="A15" s="78" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="74" t="inlineStr">
+      <c r="B15" s="79" t="inlineStr">
         <is>
           <t>STATIC | Discount 20% | v1</t>
         </is>
       </c>
-      <c r="C15" s="75" t="n">
+      <c r="C15" s="80" t="n">
         <v>7341</v>
       </c>
-      <c r="D15" s="76" t="n">
+      <c r="D15" s="81" t="n">
         <v>51</v>
       </c>
-      <c r="E15" s="75" t="n">
+      <c r="E15" s="80" t="n">
         <v>35224</v>
       </c>
       <c r="F15" s="70">
@@ -4231,7 +5153,7 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="77">
+      <c r="A17" s="82">
         <f>"Spend above is "&amp;TEXT(ROUND(SUM(C6:C15),0),"#,##0")&amp;" against "&amp;TEXT(ROUND(_Inputs!$D$13,0),"#,##0")&amp;" total ad spend — a gap means some spend sits in ads not listed here."</f>
         <v/>
       </c>
@@ -4245,14 +5167,14 @@
       <c r="I17" s="72" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="78" t="inlineStr">
+      <c r="A19" s="83" t="inlineStr">
         <is>
           <t>What to do with this table</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="73" t="inlineStr">
+      <c r="A20" s="78" t="inlineStr">
         <is>
           <t>·</t>
         </is>
@@ -4264,7 +5186,7 @@
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="73" t="inlineStr">
+      <c r="A21" s="78" t="inlineStr">
         <is>
           <t>·</t>
         </is>
@@ -4276,7 +5198,7 @@
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="73" t="inlineStr">
+      <c r="A22" s="78" t="inlineStr">
         <is>
           <t>·</t>
         </is>
@@ -4288,7 +5210,7 @@
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="73" t="inlineStr">
+      <c r="A23" s="78" t="inlineStr">
         <is>
           <t>·</t>
         </is>
@@ -4332,7 +5254,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4413,21 +5335,21 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="73" t="n">
+      <c r="A6" s="78" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="74" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>UGC-Founder</t>
         </is>
       </c>
-      <c r="C6" s="75" t="n">
+      <c r="C6" s="80" t="n">
         <v>43152</v>
       </c>
-      <c r="D6" s="76" t="n">
+      <c r="D6" s="81" t="n">
         <v>153</v>
       </c>
-      <c r="E6" s="75" t="n">
+      <c r="E6" s="80" t="n">
         <v>104431</v>
       </c>
       <c r="F6" s="70">
@@ -4448,21 +5370,21 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="73" t="n">
+      <c r="A7" s="78" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="74" t="inlineStr">
+      <c r="B7" s="79" t="inlineStr">
         <is>
           <t>Static-Bundle</t>
         </is>
       </c>
-      <c r="C7" s="75" t="n">
+      <c r="C7" s="80" t="n">
         <v>25765</v>
       </c>
-      <c r="D7" s="76" t="n">
+      <c r="D7" s="81" t="n">
         <v>89</v>
       </c>
-      <c r="E7" s="75" t="n">
+      <c r="E7" s="80" t="n">
         <v>61435</v>
       </c>
       <c r="F7" s="70">
@@ -4483,21 +5405,21 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="73" t="n">
+      <c r="A8" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="74" t="inlineStr">
+      <c r="B8" s="79" t="inlineStr">
         <is>
           <t>TT-UGC-Trend</t>
         </is>
       </c>
-      <c r="C8" s="75" t="n">
+      <c r="C8" s="80" t="n">
         <v>17270</v>
       </c>
-      <c r="D8" s="76" t="n">
+      <c r="D8" s="81" t="n">
         <v>61</v>
       </c>
-      <c r="E8" s="75" t="n">
+      <c r="E8" s="80" t="n">
         <v>37622</v>
       </c>
       <c r="F8" s="70">
@@ -4518,21 +5440,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="73" t="n">
+      <c r="A9" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="74" t="inlineStr">
+      <c r="B9" s="79" t="inlineStr">
         <is>
           <t>TT-UGC-ProbSol</t>
         </is>
       </c>
-      <c r="C9" s="75" t="n">
+      <c r="C9" s="80" t="n">
         <v>14365</v>
       </c>
-      <c r="D9" s="76" t="n">
+      <c r="D9" s="81" t="n">
         <v>69</v>
       </c>
-      <c r="E9" s="75" t="n">
+      <c r="E9" s="80" t="n">
         <v>42528</v>
       </c>
       <c r="F9" s="70">
@@ -4553,21 +5475,21 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="73" t="n">
+      <c r="A10" s="78" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="74" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>UGC-Reviews</t>
         </is>
       </c>
-      <c r="C10" s="75" t="n">
+      <c r="C10" s="80" t="n">
         <v>12497</v>
       </c>
-      <c r="D10" s="76" t="n">
+      <c r="D10" s="81" t="n">
         <v>45</v>
       </c>
-      <c r="E10" s="75" t="n">
+      <c r="E10" s="80" t="n">
         <v>31048</v>
       </c>
       <c r="F10" s="70">
@@ -4588,21 +5510,21 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="73" t="n">
+      <c r="A11" s="78" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="74" t="inlineStr">
+      <c r="B11" s="79" t="inlineStr">
         <is>
           <t>TT-Spark-CreatorA</t>
         </is>
       </c>
-      <c r="C11" s="75" t="n">
+      <c r="C11" s="80" t="n">
         <v>10640</v>
       </c>
-      <c r="D11" s="76" t="n">
+      <c r="D11" s="81" t="n">
         <v>63</v>
       </c>
-      <c r="E11" s="75" t="n">
+      <c r="E11" s="80" t="n">
         <v>38122</v>
       </c>
       <c r="F11" s="70">
@@ -4623,21 +5545,21 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="73" t="n">
+      <c r="A12" s="78" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="74" t="inlineStr">
+      <c r="B12" s="79" t="inlineStr">
         <is>
           <t>Static-Discount</t>
         </is>
       </c>
-      <c r="C12" s="75" t="n">
+      <c r="C12" s="80" t="n">
         <v>7341</v>
       </c>
-      <c r="D12" s="76" t="n">
+      <c r="D12" s="81" t="n">
         <v>51</v>
       </c>
-      <c r="E12" s="75" t="n">
+      <c r="E12" s="80" t="n">
         <v>35224</v>
       </c>
       <c r="F12" s="70">
@@ -4658,21 +5580,21 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="73" t="n">
+      <c r="A13" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="74" t="inlineStr">
+      <c r="B13" s="79" t="inlineStr">
         <is>
           <t>Carousel-Bestsellers</t>
         </is>
       </c>
-      <c r="C13" s="75" t="n">
+      <c r="C13" s="80" t="n">
         <v>5101</v>
       </c>
-      <c r="D13" s="76" t="n">
+      <c r="D13" s="81" t="n">
         <v>39</v>
       </c>
-      <c r="E13" s="75" t="n">
+      <c r="E13" s="80" t="n">
         <v>26770</v>
       </c>
       <c r="F13" s="70">
@@ -4693,7 +5615,7 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="77">
+      <c r="A15" s="82">
         <f>"Spend above is "&amp;TEXT(ROUND(SUM(C6:C13),0),"#,##0")&amp;" against "&amp;TEXT(ROUND(_Inputs!$D$13,0),"#,##0")&amp;" total ad spend — a gap means some spend sits in ads not listed here."</f>
         <v/>
       </c>
@@ -4707,14 +5629,14 @@
       <c r="I15" s="72" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="78" t="inlineStr">
+      <c r="A17" s="83" t="inlineStr">
         <is>
           <t>What to do with this table</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="73" t="inlineStr">
+      <c r="A18" s="78" t="inlineStr">
         <is>
           <t>·</t>
         </is>
@@ -4726,7 +5648,7 @@
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="73" t="inlineStr">
+      <c r="A19" s="78" t="inlineStr">
         <is>
           <t>·</t>
         </is>
@@ -4738,7 +5660,7 @@
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="73" t="inlineStr">
+      <c r="A20" s="78" t="inlineStr">
         <is>
           <t>·</t>
         </is>
@@ -4750,7 +5672,7 @@
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="73" t="inlineStr">
+      <c r="A21" s="78" t="inlineStr">
         <is>
           <t>·</t>
         </is>
@@ -4794,7 +5716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4875,21 +5797,21 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="73" t="n">
+      <c r="A6" s="78" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="74" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>Sep 15 – Sep 21</t>
         </is>
       </c>
-      <c r="C6" s="75" t="n">
+      <c r="C6" s="80" t="n">
         <v>33113</v>
       </c>
-      <c r="D6" s="76" t="n">
+      <c r="D6" s="81" t="n">
         <v>146</v>
       </c>
-      <c r="E6" s="75" t="n">
+      <c r="E6" s="80" t="n">
         <v>97068</v>
       </c>
       <c r="F6" s="70">
@@ -4910,21 +5832,21 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="73" t="n">
+      <c r="A7" s="78" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="74" t="inlineStr">
+      <c r="B7" s="79" t="inlineStr">
         <is>
           <t>Sep 29 – Sep 30</t>
         </is>
       </c>
-      <c r="C7" s="75" t="n">
+      <c r="C7" s="80" t="n">
         <v>9065</v>
       </c>
-      <c r="D7" s="76" t="n">
+      <c r="D7" s="81" t="n">
         <v>40</v>
       </c>
-      <c r="E7" s="75" t="n">
+      <c r="E7" s="80" t="n">
         <v>26355</v>
       </c>
       <c r="F7" s="70">
@@ -4945,21 +5867,21 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="73" t="n">
+      <c r="A8" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="74" t="inlineStr">
+      <c r="B8" s="79" t="inlineStr">
         <is>
           <t>Sep 8 – Sep 14</t>
         </is>
       </c>
-      <c r="C8" s="75" t="n">
+      <c r="C8" s="80" t="n">
         <v>24856</v>
       </c>
-      <c r="D8" s="76" t="n">
+      <c r="D8" s="81" t="n">
         <v>108</v>
       </c>
-      <c r="E8" s="75" t="n">
+      <c r="E8" s="80" t="n">
         <v>70754</v>
       </c>
       <c r="F8" s="70">
@@ -4980,21 +5902,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="73" t="n">
+      <c r="A9" s="78" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="74" t="inlineStr">
+      <c r="B9" s="79" t="inlineStr">
         <is>
           <t>Sep 1 – Sep 7</t>
         </is>
       </c>
-      <c r="C9" s="75" t="n">
+      <c r="C9" s="80" t="n">
         <v>35336</v>
       </c>
-      <c r="D9" s="76" t="n">
+      <c r="D9" s="81" t="n">
         <v>150</v>
       </c>
-      <c r="E9" s="75" t="n">
+      <c r="E9" s="80" t="n">
         <v>98715</v>
       </c>
       <c r="F9" s="70">
@@ -5015,21 +5937,21 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="73" t="n">
+      <c r="A10" s="78" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="74" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>Sep 22 – Sep 28</t>
         </is>
       </c>
-      <c r="C10" s="75" t="n">
+      <c r="C10" s="80" t="n">
         <v>33761</v>
       </c>
-      <c r="D10" s="76" t="n">
+      <c r="D10" s="81" t="n">
         <v>126</v>
       </c>
-      <c r="E10" s="75" t="n">
+      <c r="E10" s="80" t="n">
         <v>84288</v>
       </c>
       <c r="F10" s="70">
@@ -5086,221 +6008,4 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="31" t="inlineStr">
-        <is>
-          <t>What we did, and what happens next</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="32">
-        <f>_Inputs!$B$5&amp;"   ·   the part of the report the client actually reads"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  WHAT WE CHANGED THIS MONTH</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="79" t="inlineStr">
-        <is>
-          <t>What we changed this month</t>
-        </is>
-      </c>
-      <c r="B5" s="80">
-        <f>_Inputs!$B$56</f>
-        <v/>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
-        <is>
-          <t>Name three things you actually did. Specifics beat adjectives: "launched four UGC concepts" not "optimised creative".</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1"/>
-    <row r="7" ht="20" customHeight="1"/>
-    <row r="8" ht="20" customHeight="1"/>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  WHAT WE LEARNED</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="79" t="inlineStr">
-        <is>
-          <t>What we learned</t>
-        </is>
-      </c>
-      <c r="B11" s="80">
-        <f>_Inputs!$B$57</f>
-        <v/>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>One insight the data proved. This is what you are paid for.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1"/>
-    <row r="13" ht="20" customHeight="1"/>
-    <row r="14" ht="20" customHeight="1"/>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  WHAT WE ARE DOING NEXT MONTH</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="79" t="inlineStr">
-        <is>
-          <t>What we are doing next month</t>
-        </is>
-      </c>
-      <c r="B17" s="80">
-        <f>_Inputs!$B$58</f>
-        <v/>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>Two or three concrete moves, each tied to a number above.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1"/>
-    <row r="19" ht="20" customHeight="1"/>
-    <row r="20" ht="20" customHeight="1"/>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  WHAT THE NUMBERS DON'T SHOW</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="79" t="inlineStr">
-        <is>
-          <t>What the numbers don't show</t>
-        </is>
-      </c>
-      <c r="B23" s="80">
-        <f>_Inputs!$B$59</f>
-        <v/>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>Stockouts, shipping delays, a price change, a competitor entering. Say it before the client finds it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1"/>
-    <row r="26" ht="20" customHeight="1"/>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  WHAT WE NEED FROM YOU</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="79" t="inlineStr">
-        <is>
-          <t>What we need from you</t>
-        </is>
-      </c>
-      <c r="B29" s="80">
-        <f>_Inputs!$B$60</f>
-        <v/>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>One clear ask. New imagery, a price decision, a stock fix. Give them a job and they become a partner.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1"/>
-    <row r="31" ht="20" customHeight="1"/>
-    <row r="32" ht="20" customHeight="1"/>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  HOW TO FILL THESE IN</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="46" customHeight="1">
-      <c r="A35" s="56" t="inlineStr">
-        <is>
-          <t>Don't write these from scratch.</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>Open 05_AI_Prompts_Campaign_Performance.md and run Prompt 1 (the monthly narrative) on your _Inputs tab. It will draft all five blocks. Then edit for tone — delete anything that sounds like a machine, and cut it to half the length. The client reads the first sentence of each block.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="56" t="inlineStr">
-        <is>
-          <t>The tone rule</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>Never explain a metric the client didn't ask about. Never hide a bad month. Lead with what changed and what you're doing about it — the numbers are evidence, not the message.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="C17:C20"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="C29:C32"/>
-    <mergeCell ref="B29:B32"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="C23:C26"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A34:B34"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>